--- a/salidas/empresas/ADP.xlsx
+++ b/salidas/empresas/ADP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>21.07059669494629</v>
+        <v>21.07059288024902</v>
       </c>
       <c r="C2" t="n">
         <v>34.84723663330078</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>22.14954566955566</v>
+        <v>22.14953994750977</v>
       </c>
       <c r="C3" t="n">
         <v>36.63162994384766</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>21.99382781982422</v>
+        <v>21.99381637573242</v>
       </c>
       <c r="C4" t="n">
         <v>36.22716903686523</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>21.22346115112305</v>
+        <v>21.22345352172852</v>
       </c>
       <c r="C5" t="n">
         <v>34.9582633972168</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>21.8927173614502</v>
+        <v>21.89271354675293</v>
       </c>
       <c r="C6" t="n">
         <v>36.06062316894531</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.92367744445801</v>
+        <v>21.92369270324707</v>
       </c>
       <c r="C7" t="n">
         <v>35.96545791625977</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>21.155029296875</v>
+        <v>21.15503883361816</v>
       </c>
       <c r="C8" t="n">
         <v>34.70448684692383</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>22.81803131103516</v>
+        <v>22.81802749633789</v>
       </c>
       <c r="C9" t="n">
         <v>37.43262481689453</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>22.97515106201172</v>
+        <v>22.97515487670898</v>
       </c>
       <c r="C10" t="n">
         <v>37.54365539550781</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.99433708190918</v>
+        <v>23.99433135986328</v>
       </c>
       <c r="C11" t="n">
         <v>39.20908737182617</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>23.40710258483887</v>
+        <v>23.40709495544434</v>
       </c>
       <c r="C12" t="n">
         <v>38.24948120117188</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>24.0170841217041</v>
+        <v>24.01708793640137</v>
       </c>
       <c r="C13" t="n">
         <v>39.05840682983398</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>23.27098274230957</v>
+        <v>23.27097129821777</v>
       </c>
       <c r="C14" t="n">
         <v>37.84501647949219</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>24.26091194152832</v>
+        <v>24.26091766357422</v>
       </c>
       <c r="C15" t="n">
         <v>39.45494079589844</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>23.71435356140137</v>
+        <v>23.71434783935547</v>
       </c>
       <c r="C16" t="n">
         <v>38.38430023193359</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>24.27861213684082</v>
+        <v>24.27862167358398</v>
       </c>
       <c r="C17" t="n">
         <v>39.29763031005859</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>26.95815467834473</v>
+        <v>26.95816802978516</v>
       </c>
       <c r="C18" t="n">
         <v>43.634765625</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>26.41741943359375</v>
+        <v>26.41744422912598</v>
       </c>
       <c r="C19" t="n">
         <v>42.55487442016602</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>25.30013275146484</v>
+        <v>25.30012893676758</v>
       </c>
       <c r="C20" t="n">
         <v>40.75504684448242</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>24.92951011657715</v>
+        <v>24.92950630187988</v>
       </c>
       <c r="C21" t="n">
         <v>40.15803146362305</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>25.1630687713623</v>
+        <v>25.16305923461914</v>
       </c>
       <c r="C22" t="n">
         <v>40.32484436035156</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>27.15178871154785</v>
+        <v>27.15177726745605</v>
       </c>
       <c r="C23" t="n">
         <v>43.5118522644043</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>24.68643379211426</v>
+        <v>24.68643760681152</v>
       </c>
       <c r="C24" t="n">
         <v>39.56101989746094</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>24.55249977111816</v>
+        <v>24.55248641967773</v>
       </c>
       <c r="C25" t="n">
         <v>39.09569931030273</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>22.37457466125488</v>
+        <v>22.37457656860352</v>
       </c>
       <c r="C26" t="n">
         <v>35.62774276733398</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>22.02721214294434</v>
+        <v>22.0272159576416</v>
       </c>
       <c r="C27" t="n">
         <v>35.07462692260742</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>23.54320335388184</v>
+        <v>23.5432014465332</v>
       </c>
       <c r="C28" t="n">
         <v>37.21685791015625</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>24.54846000671387</v>
+        <v>24.54847145080566</v>
       </c>
       <c r="C29" t="n">
         <v>38.80596923828125</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>23.90977096557617</v>
+        <v>23.90976142883301</v>
       </c>
       <c r="C30" t="n">
         <v>37.79631423950195</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>23.4285888671875</v>
+        <v>23.42859077453613</v>
       </c>
       <c r="C31" t="n">
         <v>36.78665542602539</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>23.88150215148926</v>
+        <v>23.88149070739746</v>
       </c>
       <c r="C32" t="n">
         <v>37.49780654907227</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.05937576293945</v>
+        <v>24.05936813354492</v>
       </c>
       <c r="C34" t="n">
         <v>37.53292465209961</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>19.66958618164062</v>
+        <v>19.66958808898926</v>
       </c>
       <c r="C35" t="n">
         <v>30.68481063842773</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>23.10825157165527</v>
+        <v>23.10824584960938</v>
       </c>
       <c r="C36" t="n">
         <v>36.04916763305664</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>22.32860374450684</v>
+        <v>22.32859992980957</v>
       </c>
       <c r="C37" t="n">
         <v>34.53907012939453</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>20.62019157409668</v>
+        <v>20.62018585205078</v>
       </c>
       <c r="C38" t="n">
         <v>31.89640045166016</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.38286399841309</v>
+        <v>19.38286018371582</v>
       </c>
       <c r="C39" t="n">
         <v>29.98244094848633</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.17115211486816</v>
+        <v>20.1711483001709</v>
       </c>
       <c r="C41" t="n">
         <v>30.9043025970459</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.78140640258789</v>
+        <v>21.78139686584473</v>
       </c>
       <c r="C42" t="n">
         <v>33.37137985229492</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>20.48517990112305</v>
+        <v>20.48518371582031</v>
       </c>
       <c r="C43" t="n">
         <v>31.11501312255859</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>21.53140449523926</v>
+        <v>21.53140640258789</v>
       </c>
       <c r="C44" t="n">
         <v>32.70412445068359</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>22.1672420501709</v>
+        <v>22.167236328125</v>
       </c>
       <c r="C45" t="n">
         <v>33.66988754272461</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>22.91147613525391</v>
+        <v>22.91147422790527</v>
       </c>
       <c r="C46" t="n">
         <v>34.50395202636719</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>23.20296669006348</v>
+        <v>23.20296859741211</v>
       </c>
       <c r="C47" t="n">
         <v>34.94293212890625</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>25.33088111877441</v>
+        <v>25.33088684082031</v>
       </c>
       <c r="C48" t="n">
         <v>38.14749908447266</v>
@@ -1381,11 +1393,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>25.1624698638916</v>
+        <v>25.16245651245117</v>
       </c>
       <c r="C49" t="n">
         <v>37.59437942504883</v>
@@ -1406,11 +1418,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>23.96956253051758</v>
+        <v>23.96956634521484</v>
       </c>
       <c r="C50" t="n">
         <v>35.81211471557617</v>
@@ -1431,11 +1443,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>24.45143127441406</v>
+        <v>24.45142936706543</v>
       </c>
       <c r="C51" t="n">
         <v>36.53204727172852</v>
@@ -1456,11 +1468,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>26.33711242675781</v>
+        <v>26.33710479736328</v>
       </c>
       <c r="C52" t="n">
         <v>39.04301834106445</v>
@@ -1481,11 +1493,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>25.68564414978027</v>
+        <v>25.68563270568848</v>
       </c>
       <c r="C53" t="n">
         <v>38.07726287841797</v>
@@ -1506,11 +1518,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>24.21095657348633</v>
+        <v>24.21095085144043</v>
       </c>
       <c r="C54" t="n">
         <v>35.89113235473633</v>
@@ -1531,11 +1543,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>24.04275703430176</v>
+        <v>24.04275131225586</v>
       </c>
       <c r="C55" t="n">
         <v>35.34679412841797</v>
@@ -1556,7 +1568,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1581,11 +1593,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.05739402770996</v>
+        <v>23.0573902130127</v>
       </c>
       <c r="C57" t="n">
         <v>33.89815521240234</v>
@@ -1606,11 +1618,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>25.31670570373535</v>
+        <v>25.31669044494629</v>
       </c>
       <c r="C58" t="n">
         <v>36.90079116821289</v>
@@ -1631,11 +1643,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>26.79845809936523</v>
+        <v>26.79848289489746</v>
       </c>
       <c r="C59" t="n">
         <v>39.06057739257812</v>
@@ -1656,11 +1668,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>26.84665870666504</v>
+        <v>26.84666442871094</v>
       </c>
       <c r="C60" t="n">
         <v>39.13081741333008</v>
@@ -1681,11 +1693,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>28.09413909912109</v>
+        <v>28.09414100646973</v>
       </c>
       <c r="C61" t="n">
         <v>40.63213348388672</v>
@@ -1706,11 +1718,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>29.07756042480469</v>
+        <v>29.07755851745605</v>
       </c>
       <c r="C62" t="n">
         <v>42.05443572998047</v>
@@ -1731,7 +1743,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1756,11 +1768,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>31.36953163146973</v>
+        <v>31.36953735351562</v>
       </c>
       <c r="C64" t="n">
         <v>45.04828643798828</v>
@@ -1781,7 +1793,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1806,11 +1818,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>33.69276809692383</v>
+        <v>33.6927604675293</v>
       </c>
       <c r="C66" t="n">
         <v>48.38454818725586</v>
@@ -1831,11 +1843,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>32.42742538452148</v>
+        <v>32.42742919921875</v>
       </c>
       <c r="C67" t="n">
         <v>46.2510986328125</v>
@@ -1856,11 +1868,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>31.69493293762207</v>
+        <v>31.69491004943848</v>
       </c>
       <c r="C68" t="n">
         <v>45.20632171630859</v>
@@ -1881,11 +1893,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>30.79619216918945</v>
+        <v>30.79620170593262</v>
       </c>
       <c r="C69" t="n">
         <v>43.92449569702148</v>
@@ -1910,11 +1922,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>29.2426815032959</v>
+        <v>29.2426700592041</v>
       </c>
       <c r="C70" t="n">
         <v>41.39596176147461</v>
@@ -1939,11 +1951,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.4553337097168</v>
+        <v>32.45535659790039</v>
       </c>
       <c r="C71" t="n">
         <v>45.94380950927734</v>
@@ -1968,11 +1980,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>31.68628311157227</v>
+        <v>31.68629455566406</v>
       </c>
       <c r="C72" t="n">
         <v>44.85513687133789</v>
@@ -1997,11 +2009,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>33.75300598144531</v>
+        <v>33.75298690795898</v>
       </c>
       <c r="C73" t="n">
         <v>47.41878890991211</v>
@@ -2026,11 +2038,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>34.23419570922852</v>
+        <v>34.23419952392578</v>
       </c>
       <c r="C74" t="n">
         <v>48.09481811523438</v>
@@ -2055,11 +2067,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>33.94672393798828</v>
+        <v>33.94671249389648</v>
       </c>
       <c r="C75" t="n">
         <v>47.69095611572266</v>
@@ -2084,7 +2096,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2113,7 +2125,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2142,11 +2154,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>32.83129119873047</v>
+        <v>32.831298828125</v>
       </c>
       <c r="C78" t="n">
         <v>45.7857780456543</v>
@@ -2171,11 +2183,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>35.31024932861328</v>
+        <v>35.31023406982422</v>
       </c>
       <c r="C79" t="n">
         <v>48.86742782592773</v>
@@ -2200,7 +2212,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2229,11 +2241,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>36.84545135498047</v>
+        <v>36.845458984375</v>
       </c>
       <c r="C81" t="n">
         <v>50.99209976196289</v>
@@ -2258,11 +2270,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>37.46492767333984</v>
+        <v>37.46491622924805</v>
       </c>
       <c r="C82" t="n">
         <v>51.50131607055664</v>
@@ -2287,11 +2299,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>36.90925979614258</v>
+        <v>36.90927124023438</v>
       </c>
       <c r="C83" t="n">
         <v>50.73748779296875</v>
@@ -2316,11 +2328,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>36.23865127563477</v>
+        <v>36.2386589050293</v>
       </c>
       <c r="C84" t="n">
         <v>49.81562805175781</v>
@@ -2345,11 +2357,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>36.63462448120117</v>
+        <v>36.63461685180664</v>
       </c>
       <c r="C85" t="n">
         <v>49.98244094848633</v>
@@ -2374,11 +2386,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>38.15329360961914</v>
+        <v>38.15328979492188</v>
       </c>
       <c r="C86" t="n">
         <v>52.05443572998047</v>
@@ -2403,11 +2415,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>39.4853515625</v>
+        <v>39.4853401184082</v>
       </c>
       <c r="C87" t="n">
         <v>53.87181854248047</v>
@@ -2432,11 +2444,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>42.13953399658203</v>
+        <v>42.1395378112793</v>
       </c>
       <c r="C88" t="n">
         <v>57.09394073486328</v>
@@ -2461,11 +2473,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>43.63640975952148</v>
+        <v>43.63642501831055</v>
       </c>
       <c r="C89" t="n">
         <v>59.12203598022461</v>
@@ -2490,11 +2502,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>44.53065490722656</v>
+        <v>44.53067016601562</v>
       </c>
       <c r="C90" t="n">
         <v>60.33362579345703</v>
@@ -2519,11 +2531,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>44.90819549560547</v>
+        <v>44.90819931030273</v>
       </c>
       <c r="C91" t="n">
         <v>60.45653915405273</v>
@@ -2548,11 +2560,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>47.01469421386719</v>
+        <v>47.01469039916992</v>
       </c>
       <c r="C92" t="n">
         <v>63.29236221313477</v>
@@ -2577,11 +2589,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>46.40817642211914</v>
+        <v>46.40818405151367</v>
       </c>
       <c r="C93" t="n">
         <v>62.47585678100586</v>
@@ -2606,11 +2618,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>47.48394393920898</v>
+        <v>47.48393249511719</v>
       </c>
       <c r="C94" t="n">
         <v>63.54697036743164</v>
@@ -2635,11 +2647,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>49.22244262695312</v>
+        <v>49.22241592407227</v>
       </c>
       <c r="C95" t="n">
         <v>65.87357330322266</v>
@@ -2664,11 +2676,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>52.49605560302734</v>
+        <v>52.49606704711914</v>
       </c>
       <c r="C96" t="n">
         <v>70.25460815429688</v>
@@ -2693,7 +2705,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2722,11 +2734,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>50.56155014038086</v>
+        <v>50.56156158447266</v>
       </c>
       <c r="C98" t="n">
         <v>67.25197601318359</v>
@@ -2751,11 +2763,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>51.34042739868164</v>
+        <v>51.34042358398438</v>
       </c>
       <c r="C99" t="n">
         <v>68.28797149658203</v>
@@ -2780,11 +2792,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>51.31336212158203</v>
+        <v>51.31337356567383</v>
       </c>
       <c r="C100" t="n">
         <v>67.83142852783203</v>
@@ -2809,7 +2821,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2838,11 +2850,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>52.92063903808594</v>
+        <v>52.92064666748047</v>
       </c>
       <c r="C102" t="n">
         <v>69.95610046386719</v>
@@ -2867,11 +2879,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>52.97524642944336</v>
+        <v>52.97523880004883</v>
       </c>
       <c r="C103" t="n">
         <v>69.60491943359375</v>
@@ -2896,11 +2908,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>54.33168411254883</v>
+        <v>54.33169937133789</v>
       </c>
       <c r="C104" t="n">
         <v>71.38718414306641</v>
@@ -2925,11 +2937,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>55.78168106079102</v>
+        <v>55.78167724609375</v>
       </c>
       <c r="C105" t="n">
         <v>73.2923583984375</v>
@@ -2954,11 +2966,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>55.83496475219727</v>
+        <v>55.8349494934082</v>
       </c>
       <c r="C106" t="n">
         <v>72.94117736816406</v>
@@ -2983,11 +2995,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>62.60087203979492</v>
+        <v>62.60085678100586</v>
       </c>
       <c r="C107" t="n">
         <v>81.77999877929688</v>
@@ -3012,11 +3024,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>65.55562591552734</v>
+        <v>65.55563354492188</v>
       </c>
       <c r="C108" t="n">
         <v>85.63999938964844</v>
@@ -3041,11 +3053,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>64.18689727783203</v>
+        <v>64.1868896484375</v>
       </c>
       <c r="C109" t="n">
         <v>83.37000274658203</v>
@@ -3070,11 +3082,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>63.54016876220703</v>
+        <v>63.54016494750977</v>
       </c>
       <c r="C110" t="n">
         <v>82.52999877929688</v>
@@ -3099,11 +3111,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>68.39826965332031</v>
+        <v>68.39830017089844</v>
       </c>
       <c r="C111" t="n">
         <v>88.83999633789062</v>
@@ -3128,11 +3140,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>66.31619262695312</v>
+        <v>66.31620025634766</v>
       </c>
       <c r="C112" t="n">
         <v>85.63999938964844</v>
@@ -3157,11 +3169,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>65.46440124511719</v>
+        <v>65.46440887451172</v>
       </c>
       <c r="C113" t="n">
         <v>84.54000091552734</v>
@@ -3186,7 +3198,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3215,11 +3227,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>62.49515914916992</v>
+        <v>62.49514770507812</v>
       </c>
       <c r="C115" t="n">
         <v>80.23000335693359</v>
@@ -3244,11 +3256,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>62.1368293762207</v>
+        <v>62.13683700561523</v>
       </c>
       <c r="C116" t="n">
         <v>79.76999664306641</v>
@@ -3273,11 +3285,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>60.22841262817383</v>
+        <v>60.2283821105957</v>
       </c>
       <c r="C117" t="n">
         <v>77.31999969482422</v>
@@ -3302,11 +3314,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>62.99109649658203</v>
+        <v>62.99109268188477</v>
       </c>
       <c r="C118" t="n">
         <v>80.36000061035156</v>
@@ -3331,11 +3343,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>68.18811798095703</v>
+        <v>68.18807983398438</v>
       </c>
       <c r="C119" t="n">
         <v>86.98999786376953</v>
@@ -3360,11 +3372,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>67.61589050292969</v>
+        <v>67.61591339111328</v>
       </c>
       <c r="C120" t="n">
         <v>86.26000213623047</v>
@@ -3389,11 +3401,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>66.81901550292969</v>
+        <v>66.81902313232422</v>
       </c>
       <c r="C121" t="n">
         <v>84.72000122070312</v>
@@ -3418,11 +3430,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>65.53341674804688</v>
+        <v>65.53340148925781</v>
       </c>
       <c r="C122" t="n">
         <v>83.08999633789062</v>
@@ -3447,11 +3459,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>66.79535675048828</v>
+        <v>66.79536437988281</v>
       </c>
       <c r="C123" t="n">
         <v>84.69000244140625</v>
@@ -3476,11 +3488,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>71.19601440429688</v>
+        <v>71.19600677490234</v>
       </c>
       <c r="C124" t="n">
         <v>89.70999908447266</v>
@@ -3505,11 +3517,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>70.1881103515625</v>
+        <v>70.18814849853516</v>
       </c>
       <c r="C125" t="n">
         <v>88.44000244140625</v>
@@ -3534,11 +3546,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>69.71196746826172</v>
+        <v>69.71192932128906</v>
       </c>
       <c r="C126" t="n">
         <v>87.83999633789062</v>
@@ -3563,7 +3575,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3592,11 +3604,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>71.02619171142578</v>
+        <v>71.02621459960938</v>
       </c>
       <c r="C128" t="n">
         <v>88.94999694824219</v>
@@ -3621,11 +3633,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>71.71292877197266</v>
+        <v>71.712890625</v>
       </c>
       <c r="C129" t="n">
         <v>89.80999755859375</v>
@@ -3650,11 +3662,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>70.84516906738281</v>
+        <v>70.84517669677734</v>
       </c>
       <c r="C130" t="n">
         <v>88.19999694824219</v>
@@ -3679,11 +3691,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>69.92948913574219</v>
+        <v>69.92948150634766</v>
       </c>
       <c r="C131" t="n">
         <v>87.05999755859375</v>
@@ -3708,11 +3720,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>77.12648010253906</v>
+        <v>77.12646484375</v>
       </c>
       <c r="C132" t="n">
         <v>96.01999664306641</v>
@@ -3737,11 +3749,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>83.04944610595703</v>
+        <v>83.04943084716797</v>
       </c>
       <c r="C133" t="n">
         <v>102.7799987792969</v>
@@ -3766,11 +3778,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>81.60304260253906</v>
+        <v>81.60301971435547</v>
       </c>
       <c r="C134" t="n">
         <v>100.9899978637695</v>
@@ -3795,11 +3807,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>82.920166015625</v>
+        <v>82.92015075683594</v>
       </c>
       <c r="C135" t="n">
         <v>102.620002746582</v>
@@ -3824,11 +3836,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>83.18906402587891</v>
+        <v>83.18907928466797</v>
       </c>
       <c r="C136" t="n">
         <v>102.3899993896484</v>
@@ -3853,11 +3865,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>84.895263671875</v>
+        <v>84.89524841308594</v>
       </c>
       <c r="C137" t="n">
         <v>104.4899978637695</v>
@@ -3882,11 +3894,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>83.17283630371094</v>
+        <v>83.17281341552734</v>
       </c>
       <c r="C138" t="n">
         <v>102.370002746582</v>
@@ -3911,11 +3923,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>83.71745300292969</v>
+        <v>83.71747589111328</v>
       </c>
       <c r="C139" t="n">
         <v>102.4599990844727</v>
@@ -3940,7 +3952,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3969,11 +3981,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>86.99394989013672</v>
+        <v>86.99394226074219</v>
       </c>
       <c r="C141" t="n">
         <v>106.4700012207031</v>
@@ -3998,11 +4010,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>89.79634094238281</v>
+        <v>89.79629516601562</v>
       </c>
       <c r="C142" t="n">
         <v>109.3199996948242</v>
@@ -4027,11 +4039,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>95.49687957763672</v>
+        <v>95.49686431884766</v>
       </c>
       <c r="C143" t="n">
         <v>116.2600021362305</v>
@@ -4056,7 +4068,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4085,11 +4097,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>96.78681945800781</v>
+        <v>96.78681182861328</v>
       </c>
       <c r="C145" t="n">
         <v>117.1900024414062</v>
@@ -4114,11 +4126,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>102.1055679321289</v>
+        <v>102.105598449707</v>
       </c>
       <c r="C146" t="n">
         <v>123.629997253418</v>
@@ -4143,7 +4155,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4172,11 +4184,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>94.23818206787109</v>
+        <v>94.23816680908203</v>
       </c>
       <c r="C148" t="n">
         <v>113.4800033569336</v>
@@ -4201,11 +4213,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>98.05818939208984</v>
+        <v>98.05821228027344</v>
       </c>
       <c r="C149" t="n">
         <v>118.0800018310547</v>
@@ -4230,11 +4242,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>107.9736175537109</v>
+        <v>107.9736404418945</v>
       </c>
       <c r="C150" t="n">
         <v>130.0200042724609</v>
@@ -4259,11 +4271,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>111.9626541137695</v>
+        <v>111.9626770019531</v>
       </c>
       <c r="C151" t="n">
         <v>134.1399993896484</v>
@@ -4288,7 +4300,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4317,7 +4329,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4346,11 +4358,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>126.3439636230469</v>
+        <v>126.3439254760742</v>
       </c>
       <c r="C154" t="n">
         <v>150.6600036621094</v>
@@ -4375,11 +4387,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>120.8258895874023</v>
+        <v>120.8259353637695</v>
       </c>
       <c r="C155" t="n">
         <v>144.0800018310547</v>
@@ -4404,11 +4416,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>123.6268463134766</v>
+        <v>123.6268539428711</v>
       </c>
       <c r="C156" t="n">
         <v>147.4199981689453</v>
@@ -4433,11 +4445,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>110.5835494995117</v>
+        <v>110.5835723876953</v>
       </c>
       <c r="C157" t="n">
         <v>131.1199951171875</v>
@@ -4462,11 +4474,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>117.9378128051758</v>
+        <v>117.9377975463867</v>
       </c>
       <c r="C158" t="n">
         <v>139.8399963378906</v>
@@ -4491,11 +4503,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>129.0619659423828</v>
+        <v>129.0619506835938</v>
       </c>
       <c r="C159" t="n">
         <v>153.0299987792969</v>
@@ -4520,7 +4532,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4549,11 +4561,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>139.3645324707031</v>
+        <v>139.3645172119141</v>
       </c>
       <c r="C161" t="n">
         <v>164.3899993896484</v>
@@ -4578,11 +4590,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>135.7445831298828</v>
+        <v>135.7445526123047</v>
       </c>
       <c r="C162" t="n">
         <v>160.1199951171875</v>
@@ -4607,11 +4619,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>140.8348541259766</v>
+        <v>140.8348388671875</v>
       </c>
       <c r="C163" t="n">
         <v>165.3300018310547</v>
@@ -4636,11 +4648,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>141.8484954833984</v>
+        <v>141.8485717773438</v>
       </c>
       <c r="C164" t="n">
         <v>166.5200042724609</v>
@@ -4665,11 +4677,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>144.6766204833984</v>
+        <v>144.6766510009766</v>
       </c>
       <c r="C165" t="n">
         <v>169.8399963378906</v>
@@ -4694,11 +4706,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>138.1815338134766</v>
+        <v>138.1815185546875</v>
       </c>
       <c r="C166" t="n">
         <v>161.4199981689453</v>
@@ -4723,7 +4735,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4752,11 +4764,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>146.1941070556641</v>
+        <v>146.1940765380859</v>
       </c>
       <c r="C168" t="n">
         <v>170.7799987792969</v>
@@ -4781,7 +4793,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4810,7 +4822,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4839,11 +4851,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>133.1879730224609</v>
+        <v>133.1879425048828</v>
       </c>
       <c r="C171" t="n">
         <v>154.7400054931641</v>
@@ -4868,11 +4880,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>118.37109375</v>
+        <v>118.3710861206055</v>
       </c>
       <c r="C172" t="n">
         <v>136.6799926757812</v>
@@ -4897,11 +4909,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>127.0401992797852</v>
+        <v>127.0402450561523</v>
       </c>
       <c r="C173" t="n">
         <v>146.6900024414062</v>
@@ -4926,11 +4938,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>126.8669891357422</v>
+        <v>126.8670501708984</v>
       </c>
       <c r="C174" t="n">
         <v>146.4900054931641</v>
@@ -4955,11 +4967,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>129.7019195556641</v>
+        <v>129.7019348144531</v>
       </c>
       <c r="C175" t="n">
         <v>148.8899993896484</v>
@@ -4984,11 +4996,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>115.7813339233398</v>
+        <v>115.7813415527344</v>
       </c>
       <c r="C176" t="n">
         <v>132.9100036621094</v>
@@ -5013,11 +5025,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>121.1648864746094</v>
+        <v>121.164909362793</v>
       </c>
       <c r="C177" t="n">
         <v>139.0899963378906</v>
@@ -5042,7 +5054,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5071,11 +5083,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>138.5214080810547</v>
+        <v>138.5213928222656</v>
       </c>
       <c r="C179" t="n">
         <v>157.9600067138672</v>
@@ -5100,11 +5112,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>152.4822998046875</v>
+        <v>152.4822692871094</v>
       </c>
       <c r="C180" t="n">
         <v>173.8800048828125</v>
@@ -5129,7 +5141,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5158,7 +5170,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5187,11 +5199,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>153.4258117675781</v>
+        <v>153.4258728027344</v>
       </c>
       <c r="C183" t="n">
         <v>174.0200042724609</v>
@@ -5216,11 +5228,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>167.0188903808594</v>
+        <v>167.0188751220703</v>
       </c>
       <c r="C184" t="n">
         <v>188.4700012207031</v>
@@ -5245,11 +5257,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>165.7073669433594</v>
+        <v>165.7073516845703</v>
       </c>
       <c r="C185" t="n">
         <v>186.9900054931641</v>
@@ -5274,7 +5286,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5303,11 +5315,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>176.8434753417969</v>
+        <v>176.8434600830078</v>
       </c>
       <c r="C187" t="n">
         <v>198.6199951171875</v>
@@ -5332,11 +5344,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>186.6463775634766</v>
+        <v>186.6463470458984</v>
       </c>
       <c r="C188" t="n">
         <v>209.6300048828125</v>
@@ -5361,11 +5373,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>186.1210479736328</v>
+        <v>186.1210784912109</v>
       </c>
       <c r="C189" t="n">
         <v>209.0399932861328</v>
@@ -5390,11 +5402,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>178.8116302490234</v>
+        <v>178.8116455078125</v>
       </c>
       <c r="C190" t="n">
         <v>199.9199981689453</v>
@@ -5419,7 +5431,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5448,11 +5460,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>206.5117034912109</v>
+        <v>206.5116882324219</v>
       </c>
       <c r="C192" t="n">
         <v>230.8899993896484</v>
@@ -5477,7 +5489,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5506,11 +5518,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>185.223876953125</v>
+        <v>185.2238922119141</v>
       </c>
       <c r="C194" t="n">
         <v>206.1699981689453</v>
@@ -5535,7 +5547,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5564,11 +5576,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>205.4416656494141</v>
+        <v>205.4416809082031</v>
       </c>
       <c r="C196" t="n">
         <v>227.5399932861328</v>
@@ -5593,11 +5605,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>196.9906768798828</v>
+        <v>196.9906921386719</v>
       </c>
       <c r="C197" t="n">
         <v>218.1799926757812</v>
@@ -5622,7 +5634,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5651,11 +5663,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>190.5420227050781</v>
+        <v>190.5420532226562</v>
       </c>
       <c r="C199" t="n">
         <v>210.0399932861328</v>
@@ -5680,7 +5692,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5709,11 +5721,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>221.7214508056641</v>
+        <v>221.7214660644531</v>
       </c>
       <c r="C201" t="n">
         <v>244.4100036621094</v>
@@ -5738,11 +5750,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>206.0794525146484</v>
+        <v>206.0795135498047</v>
       </c>
       <c r="C202" t="n">
         <v>226.1900024414062</v>
@@ -5767,11 +5779,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>220.21044921875</v>
+        <v>220.2104949951172</v>
       </c>
       <c r="C203" t="n">
         <v>241.6999969482422</v>
@@ -5796,11 +5808,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>240.6554107666016</v>
+        <v>240.6553497314453</v>
       </c>
       <c r="C204" t="n">
         <v>264.1400146484375</v>
@@ -5825,7 +5837,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5854,11 +5866,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>206.7301483154297</v>
+        <v>206.7301635742188</v>
       </c>
       <c r="C206" t="n">
         <v>225.8099975585938</v>
@@ -5883,11 +5895,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>201.2462615966797</v>
+        <v>201.2463073730469</v>
       </c>
       <c r="C207" t="n">
         <v>219.8200073242188</v>
@@ -5912,11 +5924,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>204.9731292724609</v>
+        <v>204.9731140136719</v>
       </c>
       <c r="C208" t="n">
         <v>222.6300048828125</v>
@@ -5941,7 +5953,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5970,11 +5982,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>192.4149322509766</v>
+        <v>192.4149017333984</v>
       </c>
       <c r="C210" t="n">
         <v>208.9900054931641</v>
@@ -5999,11 +6011,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>203.5336761474609</v>
+        <v>203.5336608886719</v>
       </c>
       <c r="C211" t="n">
         <v>219.7899932861328</v>
@@ -6028,7 +6040,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6057,11 +6069,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>235.7782897949219</v>
+        <v>235.7783203125</v>
       </c>
       <c r="C213" t="n">
         <v>254.6100006103516</v>
@@ -6086,11 +6098,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>223.9008331298828</v>
+        <v>223.9008026123047</v>
       </c>
       <c r="C214" t="n">
         <v>240.5800018310547</v>
@@ -6115,11 +6127,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>203.0909881591797</v>
+        <v>203.0910186767578</v>
       </c>
       <c r="C215" t="n">
         <v>218.2200012207031</v>
@@ -6144,7 +6156,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6173,11 +6185,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>218.1327514648438</v>
+        <v>218.1327209472656</v>
       </c>
       <c r="C217" t="n">
         <v>232.9700012207031</v>
@@ -6202,7 +6214,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6231,11 +6243,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>235.1361541748047</v>
+        <v>235.1361846923828</v>
       </c>
       <c r="C219" t="n">
         <v>251.1300048828125</v>
@@ -6260,11 +6272,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>235.1854705810547</v>
+        <v>235.1854553222656</v>
       </c>
       <c r="C220" t="n">
         <v>249.7400054931641</v>
@@ -6289,7 +6301,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6318,11 +6330,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>230.6463623046875</v>
+        <v>230.6463165283203</v>
       </c>
       <c r="C222" t="n">
         <v>244.9199981689453</v>
@@ -6347,11 +6359,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>226.0751495361328</v>
+        <v>226.0751342773438</v>
       </c>
       <c r="C223" t="n">
         <v>238.6900024414062</v>
@@ -6376,11 +6388,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>248.7404327392578</v>
+        <v>248.7404174804688</v>
       </c>
       <c r="C224" t="n">
         <v>262.6199951171875</v>
@@ -6405,7 +6417,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6434,11 +6446,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>263.4294128417969</v>
+        <v>263.429443359375</v>
       </c>
       <c r="C226" t="n">
         <v>276.7300109863281</v>
@@ -6463,7 +6475,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6492,11 +6504,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>292.1779174804688</v>
+        <v>292.1778869628906</v>
       </c>
       <c r="C228" t="n">
         <v>306.9299926757812</v>
@@ -6521,11 +6533,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>280.1043090820312</v>
+        <v>280.1042785644531</v>
       </c>
       <c r="C229" t="n">
         <v>292.7300109863281</v>
@@ -6550,11 +6562,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>289.9408874511719</v>
+        <v>289.94091796875</v>
       </c>
       <c r="C230" t="n">
         <v>303.010009765625</v>
@@ -6579,7 +6591,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6608,11 +6620,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>293.9100341796875</v>
+        <v>293.9100036621094</v>
       </c>
       <c r="C232" t="n">
         <v>305.5299987792969</v>
@@ -6637,11 +6649,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>289.1675415039062</v>
+        <v>289.1675109863281</v>
       </c>
       <c r="C233" t="n">
         <v>300.6000061035156</v>
@@ -6666,7 +6678,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6695,7 +6707,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6724,7 +6736,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6753,11 +6765,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>293.9477233886719</v>
+        <v>293.9476928710938</v>
       </c>
       <c r="C237" t="n">
         <v>304.0499877929688</v>
@@ -6782,11 +6794,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>285.2220764160156</v>
+        <v>285.2221069335938</v>
       </c>
       <c r="C238" t="n">
         <v>293.5</v>
@@ -6811,11 +6823,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>252.9584503173828</v>
+        <v>252.9584655761719</v>
       </c>
       <c r="C239" t="n">
         <v>260.2999877929688</v>
@@ -6840,11 +6852,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>248.0994567871094</v>
+        <v>248.0994720458984</v>
       </c>
       <c r="C240" t="n">
         <v>255.3000030517578</v>
@@ -6869,11 +6881,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>251.5909118652344</v>
+        <v>251.5909271240234</v>
       </c>
       <c r="C241" t="n">
         <v>257.2300109863281</v>
@@ -6898,7 +6910,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6927,11 +6939,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>209.6607208251953</v>
+        <v>209.6607055664062</v>
       </c>
       <c r="C243" t="n">
         <v>214.3600006103516</v>
@@ -6956,7 +6968,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6985,7 +6997,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7014,7 +7026,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7043,7 +7055,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7072,7 +7084,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7101,7 +7113,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7130,32 +7142,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>263.6799926757812</v>
+        <v>263.1099853515625</v>
       </c>
       <c r="C250" t="n">
-        <v>263.6799926757812</v>
+        <v>263.1099853515625</v>
       </c>
       <c r="D250" t="n">
-        <v>38051100</v>
+        <v>40044700</v>
       </c>
       <c r="E250" t="n">
         <v>10.94</v>
       </c>
       <c r="F250" t="n">
-        <v>24.10237593014454</v>
+        <v>24.05027288405508</v>
       </c>
       <c r="G250" t="n">
         <v>397262737</v>
       </c>
       <c r="H250" t="n">
-        <v>104750235582.5208</v>
+        <v>104523792912.7916</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09578320958907353</v>
+        <v>0.1008015508889775</v>
       </c>
     </row>
   </sheetData>
@@ -7187,75 +7199,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7291,13 +7303,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40218</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40218</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7459,13 +7471,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7585,13 +7597,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40779</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7618,7 +7630,7 @@
       <c r="I10" t="n">
         <v>2.212467076382792</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40779</v>
       </c>
       <c r="K10" t="n">
@@ -7631,13 +7643,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7664,7 +7676,7 @@
       <c r="I11" t="n">
         <v>2.256365232660228</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K11" t="n">
@@ -7677,13 +7689,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7710,7 +7722,7 @@
       <c r="I12" t="n">
         <v>2.37928007023705</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="K12" t="n">
@@ -7723,13 +7735,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7756,7 +7768,7 @@
       <c r="I13" t="n">
         <v>2.440737489025461</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="K13" t="n">
@@ -7769,13 +7781,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41141</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7802,7 +7814,7 @@
       <c r="I14" t="n">
         <v>2.47585601404741</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41141</v>
       </c>
       <c r="K14" t="n">
@@ -7815,13 +7827,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7848,7 +7860,7 @@
       <c r="I15" t="n">
         <v>2.493415276558384</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K15" t="n">
@@ -7861,13 +7873,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41311</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7894,7 +7906,7 @@
       <c r="I16" t="n">
         <v>2.528533801580333</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41311</v>
       </c>
       <c r="K16" t="n">
@@ -7907,13 +7919,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7940,7 +7952,7 @@
       <c r="I17" t="n">
         <v>2.589991220368744</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K17" t="n">
@@ -7953,13 +7965,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41505</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7986,7 +7998,7 @@
       <c r="I18" t="n">
         <v>2.537313432835822</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41505</v>
       </c>
       <c r="K18" t="n">
@@ -7999,13 +8011,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8032,7 +8044,7 @@
       <c r="I19" t="n">
         <v>2.581211589113258</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K19" t="n">
@@ -8045,13 +8057,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41675</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8078,7 +8090,7 @@
       <c r="I20" t="n">
         <v>2.563652326602283</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41675</v>
       </c>
       <c r="K20" t="n">
@@ -8091,13 +8103,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8124,7 +8136,7 @@
       <c r="I21" t="n">
         <v>2.642669007901669</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="K21" t="n">
@@ -8137,13 +8149,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8170,7 +8182,7 @@
       <c r="I22" t="n">
         <v>2.756804214223003</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="K22" t="n">
@@ -8183,13 +8195,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8216,7 +8228,7 @@
       <c r="I23" t="n">
         <v>2.769789288849868</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="K23" t="n">
@@ -8229,13 +8241,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42040</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8262,7 +8274,7 @@
       <c r="I24" t="n">
         <v>2.774978050921861</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42040</v>
       </c>
       <c r="K24" t="n">
@@ -8275,13 +8287,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8308,7 +8320,7 @@
       <c r="I25" t="n">
         <v>2.856777875329236</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K25" t="n">
@@ -8321,13 +8333,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8354,7 +8366,7 @@
       <c r="I26" t="n">
         <v>3.05</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K26" t="n">
@@ -8367,13 +8379,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8400,7 +8412,7 @@
       <c r="I27" t="n">
         <v>3.16</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K27" t="n">
@@ -8413,13 +8425,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8446,7 +8458,7 @@
       <c r="I28" t="n">
         <v>3.21</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="K28" t="n">
@@ -8459,13 +8471,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8492,7 +8504,7 @@
       <c r="I29" t="n">
         <v>3.35</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K29" t="n">
@@ -8505,13 +8517,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8538,7 +8550,7 @@
       <c r="I30" t="n">
         <v>3.25</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K30" t="n">
@@ -8551,13 +8563,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8584,7 +8596,7 @@
       <c r="I31" t="n">
         <v>3.34</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K31" t="n">
@@ -8597,13 +8609,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8630,7 +8642,7 @@
       <c r="I32" t="n">
         <v>3.73</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="K32" t="n">
@@ -8643,13 +8655,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8676,7 +8688,7 @@
       <c r="I33" t="n">
         <v>3.87</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K33" t="n">
@@ -8689,13 +8701,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8722,7 +8734,7 @@
       <c r="I34" t="n">
         <v>3.85</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K34" t="n">
@@ -8735,13 +8747,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8768,7 +8780,7 @@
       <c r="I35" t="n">
         <v>3.94</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K35" t="n">
@@ -8781,13 +8793,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8814,7 +8826,7 @@
       <c r="I36" t="n">
         <v>3.86</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="K36" t="n">
@@ -8827,13 +8839,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8860,7 +8872,7 @@
       <c r="I37" t="n">
         <v>4</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K37" t="n">
@@ -8873,13 +8885,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8906,7 +8918,7 @@
       <c r="I38" t="n">
         <v>3.66</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K38" t="n">
@@ -8919,13 +8931,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8952,7 +8964,7 @@
       <c r="I39" t="n">
         <v>3.91</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="K39" t="n">
@@ -8965,13 +8977,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8998,7 +9010,7 @@
       <c r="I40" t="n">
         <v>4.13</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="K40" t="n">
@@ -9011,13 +9023,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9044,7 +9056,7 @@
       <c r="I41" t="n">
         <v>4.409999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K41" t="n">
@@ -9057,13 +9069,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9090,7 +9102,7 @@
       <c r="I42" t="n">
         <v>5.239999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="K42" t="n">
@@ -9103,13 +9115,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9136,7 +9148,7 @@
       <c r="I43" t="n">
         <v>5.43</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="K43" t="n">
@@ -9149,13 +9161,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9182,7 +9194,7 @@
       <c r="I44" t="n">
         <v>5.66</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="K44" t="n">
@@ -9195,13 +9207,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9228,7 +9240,7 @@
       <c r="I45" t="n">
         <v>5.83</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K45" t="n">
@@ -9241,13 +9253,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9274,7 +9286,7 @@
       <c r="I46" t="n">
         <v>5.7</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K46" t="n">
@@ -9287,13 +9299,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9320,7 +9332,7 @@
       <c r="I47" t="n">
         <v>5.76</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K47" t="n">
@@ -9333,13 +9345,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9366,7 +9378,7 @@
       <c r="I48" t="n">
         <v>5.77</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="K48" t="n">
@@ -9379,13 +9391,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9412,7 +9424,7 @@
       <c r="I49" t="n">
         <v>5.77</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K49" t="n">
@@ -9425,13 +9437,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9458,7 +9470,7 @@
       <c r="I50" t="n">
         <v>6.069999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="K50" t="n">
@@ -9471,13 +9483,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9504,7 +9516,7 @@
       <c r="I51" t="n">
         <v>6.32</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K51" t="n">
@@ -9517,13 +9529,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9550,7 +9562,7 @@
       <c r="I52" t="n">
         <v>6.459999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="K52" t="n">
@@ -9563,13 +9575,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9596,7 +9608,7 @@
       <c r="I53" t="n">
         <v>6.77</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K53" t="n">
@@ -9609,13 +9621,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9642,7 +9654,7 @@
       <c r="I54" t="n">
         <v>7</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K54" t="n">
@@ -9655,13 +9667,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9688,7 +9700,7 @@
       <c r="I55" t="n">
         <v>7.22</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K55" t="n">
@@ -9701,13 +9713,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9734,7 +9746,7 @@
       <c r="I56" t="n">
         <v>7.52</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="K56" t="n">
@@ -9747,13 +9759,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9780,7 +9792,7 @@
       <c r="I57" t="n">
         <v>7.82</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="K57" t="n">
@@ -9793,13 +9805,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9826,7 +9838,7 @@
       <c r="I58" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K58" t="n">
@@ -9839,13 +9851,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9872,7 +9884,7 @@
       <c r="I59" t="n">
         <v>8.420000000000002</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K59" t="n">
@@ -9885,13 +9897,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9918,7 +9930,7 @@
       <c r="I60" t="n">
         <v>8.600000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="K60" t="n">
@@ -9931,13 +9943,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9964,7 +9976,7 @@
       <c r="I61" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K61" t="n">
@@ -9977,13 +9989,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10010,7 +10022,7 @@
       <c r="I62" t="n">
         <v>9.1</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K62" t="n">
@@ -10023,13 +10035,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10056,7 +10068,7 @@
       <c r="I63" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K63" t="n">
@@ -10069,13 +10081,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10102,7 +10114,7 @@
       <c r="I64" t="n">
         <v>9.58</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="K64" t="n">
@@ -10115,13 +10127,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10148,7 +10160,7 @@
       <c r="I65" t="n">
         <v>9.76</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K65" t="n">
@@ -10161,13 +10173,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10194,7 +10206,7 @@
       <c r="I66" t="n">
         <v>9.98</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K66" t="n">
@@ -10207,13 +10219,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10240,7 +10252,7 @@
       <c r="I67" t="n">
         <v>10.13</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K67" t="n">
@@ -10253,13 +10265,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10286,7 +10298,7 @@
       <c r="I68" t="n">
         <v>10.4</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="K68" t="n">
@@ -10299,13 +10311,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10332,7 +10344,7 @@
       <c r="I69" t="n">
         <v>10.72</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K69" t="n">
@@ -10345,13 +10357,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10378,7 +10390,7 @@
       <c r="I70" t="n">
         <v>10.94</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K70" t="n">
@@ -10415,52 +10427,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C2" t="n">
@@ -10489,10 +10501,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40218</v>
       </c>
       <c r="C3" t="n">
@@ -10521,10 +10533,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40410</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40415</v>
       </c>
       <c r="C4" t="n">
@@ -10553,10 +10565,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="C5" t="n">
@@ -10585,10 +10597,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40583</v>
       </c>
       <c r="C6" t="n">
@@ -10617,10 +10629,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C7" t="n">
@@ -10649,10 +10661,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40767</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40779</v>
       </c>
       <c r="C8" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C9" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40946</v>
       </c>
       <c r="C10" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41033</v>
       </c>
       <c r="C11" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41131</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41141</v>
       </c>
       <c r="C12" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41211</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C13" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41311</v>
       </c>
       <c r="C14" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C15" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41495</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41505</v>
       </c>
       <c r="C16" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41576</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C17" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41675</v>
       </c>
       <c r="C18" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41757</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C19" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C20" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41936</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41942</v>
       </c>
       <c r="C21" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42040</v>
       </c>
       <c r="C22" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C23" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C24" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C25" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42403</v>
       </c>
       <c r="C26" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C27" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C28" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C29" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42762</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="C30" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C31" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C32" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C33" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43126</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="C34" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C35" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C36" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C37" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43490</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="C38" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C39" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="C40" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43768</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="C41" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43858</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="C42" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43949</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C43" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C44" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44131</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C45" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44223</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="C46" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44313</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C47" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44412</v>
       </c>
       <c r="C48" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44495</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C49" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44587</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="C50" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44677</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C51" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C52" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C53" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="C54" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45043</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="C55" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C56" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C57" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45320</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="C58" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C59" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45506</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C60" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45594</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C61" t="n">
@@ -12377,10 +12389,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45684</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45687</v>
       </c>
       <c r="C62" t="n">
@@ -12409,10 +12421,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C63" t="n">
@@ -12441,10 +12453,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C64" t="n">
@@ -12473,10 +12485,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45958</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C65" t="n">
@@ -12505,10 +12517,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46048</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46051</v>
       </c>
       <c r="C66" t="n">
@@ -12537,10 +12549,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C67" t="n">
@@ -12569,10 +12581,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C68" t="n">
@@ -12619,12 +12631,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/ADP.xlsx
+++ b/salidas/empresas/ADP.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>21.07059288024902</v>
+        <v>21.07059669494629</v>
       </c>
       <c r="C2" t="n">
         <v>34.84723663330078</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>21.99381637573242</v>
+        <v>21.99382591247559</v>
       </c>
       <c r="C4" t="n">
         <v>36.22716903686523</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>21.22345352172852</v>
+        <v>21.22345924377441</v>
       </c>
       <c r="C5" t="n">
         <v>34.9582633972168</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>21.89271354675293</v>
+        <v>21.89270973205566</v>
       </c>
       <c r="C6" t="n">
         <v>36.06062316894531</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.92369270324707</v>
+        <v>21.9236888885498</v>
       </c>
       <c r="C7" t="n">
         <v>35.96545791625977</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>21.15503883361816</v>
+        <v>21.155029296875</v>
       </c>
       <c r="C8" t="n">
         <v>34.70448684692383</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>22.81802749633789</v>
+        <v>22.81804275512695</v>
       </c>
       <c r="C9" t="n">
         <v>37.43262481689453</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>22.97515487670898</v>
+        <v>22.97517013549805</v>
       </c>
       <c r="C10" t="n">
         <v>37.54365539550781</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.99433135986328</v>
+        <v>23.99434089660645</v>
       </c>
       <c r="C11" t="n">
         <v>39.20908737182617</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>23.40709495544434</v>
+        <v>23.40710067749023</v>
       </c>
       <c r="C12" t="n">
         <v>38.24948120117188</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>24.01708793640137</v>
+        <v>24.01708602905273</v>
       </c>
       <c r="C13" t="n">
         <v>39.05840682983398</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>24.26091766357422</v>
+        <v>24.26092147827148</v>
       </c>
       <c r="C15" t="n">
         <v>39.45494079589844</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>23.71434783935547</v>
+        <v>23.71435546875</v>
       </c>
       <c r="C16" t="n">
         <v>38.38430023193359</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>26.95816802978516</v>
+        <v>26.95815086364746</v>
       </c>
       <c r="C18" t="n">
         <v>43.634765625</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>26.41744422912598</v>
+        <v>26.41743087768555</v>
       </c>
       <c r="C19" t="n">
         <v>42.55487442016602</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>25.16305923461914</v>
+        <v>25.16306686401367</v>
       </c>
       <c r="C22" t="n">
         <v>40.32484436035156</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>27.15177726745605</v>
+        <v>27.15178298950195</v>
       </c>
       <c r="C23" t="n">
         <v>43.5118522644043</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>24.68643760681152</v>
+        <v>24.68642997741699</v>
       </c>
       <c r="C24" t="n">
         <v>39.56101989746094</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>24.55248641967773</v>
+        <v>24.5524845123291</v>
       </c>
       <c r="C25" t="n">
         <v>39.09569931030273</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>22.37457656860352</v>
+        <v>22.37457466125488</v>
       </c>
       <c r="C26" t="n">
         <v>35.62774276733398</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>22.0272159576416</v>
+        <v>22.0272102355957</v>
       </c>
       <c r="C27" t="n">
         <v>35.07462692260742</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>23.5432014465332</v>
+        <v>23.54320526123047</v>
       </c>
       <c r="C28" t="n">
         <v>37.21685791015625</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>24.54847145080566</v>
+        <v>24.54845809936523</v>
       </c>
       <c r="C29" t="n">
         <v>38.80596923828125</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>23.90976142883301</v>
+        <v>23.90975761413574</v>
       </c>
       <c r="C30" t="n">
         <v>37.79631423950195</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>23.42859077453613</v>
+        <v>23.4285831451416</v>
       </c>
       <c r="C31" t="n">
         <v>36.78665542602539</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>23.88149070739746</v>
+        <v>23.88150978088379</v>
       </c>
       <c r="C32" t="n">
         <v>37.49780654907227</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>24.81530380249023</v>
+        <v>24.81529426574707</v>
       </c>
       <c r="C33" t="n">
         <v>38.96400451660156</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.05936813354492</v>
+        <v>24.05937004089355</v>
       </c>
       <c r="C34" t="n">
         <v>37.53292465209961</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>19.66958808898926</v>
+        <v>19.66959190368652</v>
       </c>
       <c r="C35" t="n">
         <v>30.68481063842773</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>23.10824584960938</v>
+        <v>23.10825157165527</v>
       </c>
       <c r="C36" t="n">
         <v>36.04916763305664</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>22.32859992980957</v>
+        <v>22.3286018371582</v>
       </c>
       <c r="C37" t="n">
         <v>34.53907012939453</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>20.62018585205078</v>
+        <v>20.62018775939941</v>
       </c>
       <c r="C38" t="n">
         <v>31.89640045166016</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.38286018371582</v>
+        <v>19.38286781311035</v>
       </c>
       <c r="C39" t="n">
         <v>29.98244094848633</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>20.14822387695312</v>
+        <v>20.14823150634766</v>
       </c>
       <c r="C40" t="n">
         <v>30.86918258666992</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.1711483001709</v>
+        <v>20.17115020751953</v>
       </c>
       <c r="C41" t="n">
         <v>30.9043025970459</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.78139686584473</v>
+        <v>21.78140258789062</v>
       </c>
       <c r="C42" t="n">
         <v>33.37137985229492</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>20.48518371582031</v>
+        <v>20.48517799377441</v>
       </c>
       <c r="C43" t="n">
         <v>31.11501312255859</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>21.53140640258789</v>
+        <v>21.53140068054199</v>
       </c>
       <c r="C44" t="n">
         <v>32.70412445068359</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>22.167236328125</v>
+        <v>22.16723442077637</v>
       </c>
       <c r="C45" t="n">
         <v>33.66988754272461</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>22.91147422790527</v>
+        <v>22.9114818572998</v>
       </c>
       <c r="C46" t="n">
         <v>34.50395202636719</v>
@@ -1397,7 +1397,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>25.16245651245117</v>
+        <v>25.1624641418457</v>
       </c>
       <c r="C49" t="n">
         <v>37.59437942504883</v>
@@ -1422,7 +1422,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>23.96956634521484</v>
+        <v>23.96956253051758</v>
       </c>
       <c r="C50" t="n">
         <v>35.81211471557617</v>
@@ -1472,7 +1472,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>26.33710479736328</v>
+        <v>26.33711433410645</v>
       </c>
       <c r="C52" t="n">
         <v>39.04301834106445</v>
@@ -1497,7 +1497,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>25.68563270568848</v>
+        <v>25.68564224243164</v>
       </c>
       <c r="C53" t="n">
         <v>38.07726287841797</v>
@@ -1572,7 +1572,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>24.64591407775879</v>
+        <v>24.64590835571289</v>
       </c>
       <c r="C56" t="n">
         <v>36.23353958129883</v>
@@ -1597,7 +1597,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.0573902130127</v>
+        <v>23.05739593505859</v>
       </c>
       <c r="C57" t="n">
         <v>33.89815521240234</v>
@@ -1622,7 +1622,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>25.31669044494629</v>
+        <v>25.31669616699219</v>
       </c>
       <c r="C58" t="n">
         <v>36.90079116821289</v>
@@ -1647,7 +1647,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>26.79848289489746</v>
+        <v>26.79847526550293</v>
       </c>
       <c r="C59" t="n">
         <v>39.06057739257812</v>
@@ -1697,7 +1697,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>28.09414100646973</v>
+        <v>28.09414672851562</v>
       </c>
       <c r="C61" t="n">
         <v>40.63213348388672</v>
@@ -1722,7 +1722,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>29.07755851745605</v>
+        <v>29.07755470275879</v>
       </c>
       <c r="C62" t="n">
         <v>42.05443572998047</v>
@@ -1772,7 +1772,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>31.36953735351562</v>
+        <v>31.36954116821289</v>
       </c>
       <c r="C64" t="n">
         <v>45.04828643798828</v>
@@ -1797,7 +1797,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>33.23421859741211</v>
+        <v>33.23422241210938</v>
       </c>
       <c r="C65" t="n">
         <v>47.72607421875</v>
@@ -1822,7 +1822,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>33.6927604675293</v>
+        <v>33.69276428222656</v>
       </c>
       <c r="C66" t="n">
         <v>48.38454818725586</v>
@@ -1847,7 +1847,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>32.42742919921875</v>
+        <v>32.42742156982422</v>
       </c>
       <c r="C67" t="n">
         <v>46.2510986328125</v>
@@ -1872,7 +1872,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>31.69491004943848</v>
+        <v>31.69490814208984</v>
       </c>
       <c r="C68" t="n">
         <v>45.20632171630859</v>
@@ -1926,7 +1926,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>29.2426700592041</v>
+        <v>29.24267959594727</v>
       </c>
       <c r="C70" t="n">
         <v>41.39596176147461</v>
@@ -1955,7 +1955,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.45535659790039</v>
+        <v>32.45533752441406</v>
       </c>
       <c r="C71" t="n">
         <v>45.94380950927734</v>
@@ -1984,7 +1984,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>31.68629455566406</v>
+        <v>31.68627548217773</v>
       </c>
       <c r="C72" t="n">
         <v>44.85513687133789</v>
@@ -2013,7 +2013,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>33.75298690795898</v>
+        <v>33.75297927856445</v>
       </c>
       <c r="C73" t="n">
         <v>47.41878890991211</v>
@@ -2071,7 +2071,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>33.94671249389648</v>
+        <v>33.94672012329102</v>
       </c>
       <c r="C75" t="n">
         <v>47.69095611572266</v>
@@ -2129,7 +2129,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>35.01583862304688</v>
+        <v>35.01584243774414</v>
       </c>
       <c r="C77" t="n">
         <v>48.83230972290039</v>
@@ -2158,7 +2158,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>32.831298828125</v>
+        <v>32.83128356933594</v>
       </c>
       <c r="C78" t="n">
         <v>45.7857780456543</v>
@@ -2187,7 +2187,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>35.31023406982422</v>
+        <v>35.31023788452148</v>
       </c>
       <c r="C79" t="n">
         <v>48.86742782592773</v>
@@ -2216,7 +2216,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>35.87484359741211</v>
+        <v>35.87484741210938</v>
       </c>
       <c r="C80" t="n">
         <v>49.6488151550293</v>
@@ -2245,7 +2245,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>36.845458984375</v>
+        <v>36.84546661376953</v>
       </c>
       <c r="C81" t="n">
         <v>50.99209976196289</v>
@@ -2274,7 +2274,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>37.46491622924805</v>
+        <v>37.46490859985352</v>
       </c>
       <c r="C82" t="n">
         <v>51.50131607055664</v>
@@ -2303,7 +2303,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>36.90927124023438</v>
+        <v>36.90926361083984</v>
       </c>
       <c r="C83" t="n">
         <v>50.73748779296875</v>
@@ -2332,7 +2332,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>36.2386589050293</v>
+        <v>36.23867034912109</v>
       </c>
       <c r="C84" t="n">
         <v>49.81562805175781</v>
@@ -2390,7 +2390,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>38.15328979492188</v>
+        <v>38.15328598022461</v>
       </c>
       <c r="C86" t="n">
         <v>52.05443572998047</v>
@@ -2419,7 +2419,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>39.4853401184082</v>
+        <v>39.48533630371094</v>
       </c>
       <c r="C87" t="n">
         <v>53.87181854248047</v>
@@ -2448,7 +2448,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>42.1395378112793</v>
+        <v>42.13953018188477</v>
       </c>
       <c r="C88" t="n">
         <v>57.09394073486328</v>
@@ -2477,7 +2477,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>43.63642501831055</v>
+        <v>43.63642120361328</v>
       </c>
       <c r="C89" t="n">
         <v>59.12203598022461</v>
@@ -2506,7 +2506,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>44.53067016601562</v>
+        <v>44.53066253662109</v>
       </c>
       <c r="C90" t="n">
         <v>60.33362579345703</v>
@@ -2535,7 +2535,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>44.90819931030273</v>
+        <v>44.90818786621094</v>
       </c>
       <c r="C91" t="n">
         <v>60.45653915405273</v>
@@ -2564,7 +2564,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>47.01469039916992</v>
+        <v>47.01470565795898</v>
       </c>
       <c r="C92" t="n">
         <v>63.29236221313477</v>
@@ -2593,7 +2593,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>46.40818405151367</v>
+        <v>46.40818023681641</v>
       </c>
       <c r="C93" t="n">
         <v>62.47585678100586</v>
@@ -2622,7 +2622,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>47.48393249511719</v>
+        <v>47.48393630981445</v>
       </c>
       <c r="C94" t="n">
         <v>63.54697036743164</v>
@@ -2651,7 +2651,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>49.22241592407227</v>
+        <v>49.22244644165039</v>
       </c>
       <c r="C95" t="n">
         <v>65.87357330322266</v>
@@ -2680,7 +2680,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>52.49606704711914</v>
+        <v>52.49605560302734</v>
       </c>
       <c r="C96" t="n">
         <v>70.25460815429688</v>
@@ -2709,7 +2709,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>53.33384323120117</v>
+        <v>53.33385848999023</v>
       </c>
       <c r="C97" t="n">
         <v>70.93942260742188</v>
@@ -2738,7 +2738,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>50.56156158447266</v>
+        <v>50.56153106689453</v>
       </c>
       <c r="C98" t="n">
         <v>67.25197601318359</v>
@@ -2767,7 +2767,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>51.34042358398438</v>
+        <v>51.34043884277344</v>
       </c>
       <c r="C99" t="n">
         <v>68.28797149658203</v>
@@ -2796,7 +2796,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>51.31337356567383</v>
+        <v>51.31336212158203</v>
       </c>
       <c r="C100" t="n">
         <v>67.83142852783203</v>
@@ -2825,7 +2825,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>51.77827835083008</v>
+        <v>51.77828979492188</v>
       </c>
       <c r="C101" t="n">
         <v>68.44600677490234</v>
@@ -2854,7 +2854,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>52.92064666748047</v>
+        <v>52.92062377929688</v>
       </c>
       <c r="C102" t="n">
         <v>69.95610046386719</v>
@@ -2912,7 +2912,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>54.33169937133789</v>
+        <v>54.3316764831543</v>
       </c>
       <c r="C104" t="n">
         <v>71.38718414306641</v>
@@ -2941,7 +2941,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>55.78167724609375</v>
+        <v>55.78168869018555</v>
       </c>
       <c r="C105" t="n">
         <v>73.2923583984375</v>
@@ -2970,7 +2970,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>55.8349494934082</v>
+        <v>55.83495330810547</v>
       </c>
       <c r="C106" t="n">
         <v>72.94117736816406</v>
@@ -2999,7 +2999,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>62.60085678100586</v>
+        <v>62.60087966918945</v>
       </c>
       <c r="C107" t="n">
         <v>81.77999877929688</v>
@@ -3028,7 +3028,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>65.55563354492188</v>
+        <v>65.55561828613281</v>
       </c>
       <c r="C108" t="n">
         <v>85.63999938964844</v>
@@ -3057,7 +3057,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>64.1868896484375</v>
+        <v>64.18691253662109</v>
       </c>
       <c r="C109" t="n">
         <v>83.37000274658203</v>
@@ -3086,7 +3086,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>63.54016494750977</v>
+        <v>63.54017639160156</v>
       </c>
       <c r="C110" t="n">
         <v>82.52999877929688</v>
@@ -3115,7 +3115,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>68.39830017089844</v>
+        <v>68.39826965332031</v>
       </c>
       <c r="C111" t="n">
         <v>88.83999633789062</v>
@@ -3144,7 +3144,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>66.31620025634766</v>
+        <v>66.31616973876953</v>
       </c>
       <c r="C112" t="n">
         <v>85.63999938964844</v>
@@ -3173,7 +3173,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>65.46440887451172</v>
+        <v>65.46439361572266</v>
       </c>
       <c r="C113" t="n">
         <v>84.54000091552734</v>
@@ -3202,7 +3202,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>66.21553802490234</v>
+        <v>66.21552276611328</v>
       </c>
       <c r="C114" t="n">
         <v>85.51000213623047</v>
@@ -3231,7 +3231,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>62.49514770507812</v>
+        <v>62.49514007568359</v>
       </c>
       <c r="C115" t="n">
         <v>80.23000335693359</v>
@@ -3260,7 +3260,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>62.13683700561523</v>
+        <v>62.1368293762207</v>
       </c>
       <c r="C116" t="n">
         <v>79.76999664306641</v>
@@ -3289,7 +3289,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>60.2283821105957</v>
+        <v>60.2283935546875</v>
       </c>
       <c r="C117" t="n">
         <v>77.31999969482422</v>
@@ -3318,7 +3318,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>62.99109268188477</v>
+        <v>62.99111938476562</v>
       </c>
       <c r="C118" t="n">
         <v>80.36000061035156</v>
@@ -3347,7 +3347,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>68.18807983398438</v>
+        <v>68.18811798095703</v>
       </c>
       <c r="C119" t="n">
         <v>86.98999786376953</v>
@@ -3376,7 +3376,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>67.61591339111328</v>
+        <v>67.61587524414062</v>
       </c>
       <c r="C120" t="n">
         <v>86.26000213623047</v>
@@ -3405,7 +3405,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>66.81902313232422</v>
+        <v>66.81900787353516</v>
       </c>
       <c r="C121" t="n">
         <v>84.72000122070312</v>
@@ -3434,7 +3434,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>65.53340148925781</v>
+        <v>65.53342437744141</v>
       </c>
       <c r="C122" t="n">
         <v>83.08999633789062</v>
@@ -3463,7 +3463,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>66.79536437988281</v>
+        <v>66.79533386230469</v>
       </c>
       <c r="C123" t="n">
         <v>84.69000244140625</v>
@@ -3492,7 +3492,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>71.19600677490234</v>
+        <v>71.19602203369141</v>
       </c>
       <c r="C124" t="n">
         <v>89.70999908447266</v>
@@ -3521,7 +3521,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>70.18814849853516</v>
+        <v>70.18811798095703</v>
       </c>
       <c r="C125" t="n">
         <v>88.44000244140625</v>
@@ -3550,7 +3550,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>69.71192932128906</v>
+        <v>69.71195220947266</v>
       </c>
       <c r="C126" t="n">
         <v>87.83999633789062</v>
@@ -3579,7 +3579,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>73.35782623291016</v>
+        <v>73.35780334472656</v>
       </c>
       <c r="C127" t="n">
         <v>91.87000274658203</v>
@@ -3608,7 +3608,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>71.02621459960938</v>
+        <v>71.02622222900391</v>
       </c>
       <c r="C128" t="n">
         <v>88.94999694824219</v>
@@ -3695,7 +3695,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>69.92948150634766</v>
+        <v>69.92948913574219</v>
       </c>
       <c r="C131" t="n">
         <v>87.05999755859375</v>
@@ -3724,7 +3724,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>77.12646484375</v>
+        <v>77.12645721435547</v>
       </c>
       <c r="C132" t="n">
         <v>96.01999664306641</v>
@@ -3782,7 +3782,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>81.60301971435547</v>
+        <v>81.60305023193359</v>
       </c>
       <c r="C134" t="n">
         <v>100.9899978637695</v>
@@ -3811,7 +3811,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>82.92015075683594</v>
+        <v>82.92014312744141</v>
       </c>
       <c r="C135" t="n">
         <v>102.620002746582</v>
@@ -3840,7 +3840,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>83.18907928466797</v>
+        <v>83.18904876708984</v>
       </c>
       <c r="C136" t="n">
         <v>102.3899993896484</v>
@@ -3898,7 +3898,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>83.17281341552734</v>
+        <v>83.17282867431641</v>
       </c>
       <c r="C138" t="n">
         <v>102.370002746582</v>
@@ -3927,7 +3927,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>83.71747589111328</v>
+        <v>83.71745300292969</v>
       </c>
       <c r="C139" t="n">
         <v>102.4599990844727</v>
@@ -3956,7 +3956,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>97.15835571289062</v>
+        <v>97.15834045410156</v>
       </c>
       <c r="C140" t="n">
         <v>118.9100036621094</v>
@@ -4014,7 +4014,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>89.79629516601562</v>
+        <v>89.79630279541016</v>
       </c>
       <c r="C142" t="n">
         <v>109.3199996948242</v>
@@ -4043,7 +4043,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>95.49686431884766</v>
+        <v>95.49687957763672</v>
       </c>
       <c r="C143" t="n">
         <v>116.2600021362305</v>
@@ -4072,7 +4072,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>94.01835632324219</v>
+        <v>94.01834106445312</v>
       </c>
       <c r="C144" t="n">
         <v>114.4599990844727</v>
@@ -4101,7 +4101,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>96.78681182861328</v>
+        <v>96.78680419921875</v>
       </c>
       <c r="C145" t="n">
         <v>117.1900024414062</v>
@@ -4130,7 +4130,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>102.105598449707</v>
+        <v>102.1055603027344</v>
       </c>
       <c r="C146" t="n">
         <v>123.629997253418</v>
@@ -4159,7 +4159,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>95.24237823486328</v>
+        <v>95.24235534667969</v>
       </c>
       <c r="C147" t="n">
         <v>115.3199996948242</v>
@@ -4217,7 +4217,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>98.05821228027344</v>
+        <v>98.05818176269531</v>
       </c>
       <c r="C149" t="n">
         <v>118.0800018310547</v>
@@ -4275,7 +4275,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>111.9626770019531</v>
+        <v>111.962646484375</v>
       </c>
       <c r="C151" t="n">
         <v>134.1399993896484</v>
@@ -4333,7 +4333,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>122.4878616333008</v>
+        <v>122.4878005981445</v>
       </c>
       <c r="C153" t="n">
         <v>146.75</v>
@@ -4362,7 +4362,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>126.3439254760742</v>
+        <v>126.3439407348633</v>
       </c>
       <c r="C154" t="n">
         <v>150.6600036621094</v>
@@ -4391,7 +4391,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>120.8259353637695</v>
+        <v>120.825927734375</v>
       </c>
       <c r="C155" t="n">
         <v>144.0800018310547</v>
@@ -4420,7 +4420,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>123.6268539428711</v>
+        <v>123.6268615722656</v>
       </c>
       <c r="C156" t="n">
         <v>147.4199981689453</v>
@@ -4449,7 +4449,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>110.5835723876953</v>
+        <v>110.5835266113281</v>
       </c>
       <c r="C157" t="n">
         <v>131.1199951171875</v>
@@ -4478,7 +4478,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>117.9377975463867</v>
+        <v>117.9378051757812</v>
       </c>
       <c r="C158" t="n">
         <v>139.8399963378906</v>
@@ -4594,7 +4594,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>135.7445526123047</v>
+        <v>135.7445373535156</v>
       </c>
       <c r="C162" t="n">
         <v>160.1199951171875</v>
@@ -4652,7 +4652,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>141.8485717773438</v>
+        <v>141.8485412597656</v>
       </c>
       <c r="C164" t="n">
         <v>166.5200042724609</v>
@@ -4681,7 +4681,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>144.6766510009766</v>
+        <v>144.6766204833984</v>
       </c>
       <c r="C165" t="n">
         <v>169.8399963378906</v>
@@ -4710,7 +4710,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>138.1815185546875</v>
+        <v>138.1816101074219</v>
       </c>
       <c r="C166" t="n">
         <v>161.4199981689453</v>
@@ -4739,7 +4739,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>138.8749389648438</v>
+        <v>138.8749237060547</v>
       </c>
       <c r="C167" t="n">
         <v>162.2299957275391</v>
@@ -4826,7 +4826,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>147.5189514160156</v>
+        <v>147.5189361572266</v>
       </c>
       <c r="C170" t="n">
         <v>171.3899993896484</v>
@@ -4884,7 +4884,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>118.3710861206055</v>
+        <v>118.3711166381836</v>
       </c>
       <c r="C172" t="n">
         <v>136.6799926757812</v>
@@ -4913,7 +4913,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>127.0402450561523</v>
+        <v>127.0402145385742</v>
       </c>
       <c r="C173" t="n">
         <v>146.6900024414062</v>
@@ -4942,7 +4942,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>126.8670501708984</v>
+        <v>126.8670120239258</v>
       </c>
       <c r="C174" t="n">
         <v>146.4900054931641</v>
@@ -4971,7 +4971,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>129.7019348144531</v>
+        <v>129.7019195556641</v>
       </c>
       <c r="C175" t="n">
         <v>148.8899993896484</v>
@@ -5029,7 +5029,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>121.164909362793</v>
+        <v>121.1648406982422</v>
       </c>
       <c r="C177" t="n">
         <v>139.0899963378906</v>
@@ -5058,7 +5058,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>122.3243179321289</v>
+        <v>122.3243026733398</v>
       </c>
       <c r="C178" t="n">
         <v>139.4900054931641</v>
@@ -5116,7 +5116,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>152.4822692871094</v>
+        <v>152.4822845458984</v>
       </c>
       <c r="C180" t="n">
         <v>173.8800048828125</v>
@@ -5145,7 +5145,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>155.3478698730469</v>
+        <v>155.3478546142578</v>
       </c>
       <c r="C181" t="n">
         <v>176.1999969482422</v>
@@ -5174,7 +5174,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>145.5791015625</v>
+        <v>145.5790863037109</v>
       </c>
       <c r="C182" t="n">
         <v>165.1199951171875</v>
@@ -5232,7 +5232,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>167.0188751220703</v>
+        <v>167.0188903808594</v>
       </c>
       <c r="C184" t="n">
         <v>188.4700012207031</v>
@@ -5261,7 +5261,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>165.7073516845703</v>
+        <v>165.7073669433594</v>
       </c>
       <c r="C185" t="n">
         <v>186.9900054931641</v>
@@ -5290,7 +5290,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>173.7095794677734</v>
+        <v>173.7095947265625</v>
       </c>
       <c r="C186" t="n">
         <v>196.0200042724609</v>
@@ -5319,7 +5319,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>176.8434600830078</v>
+        <v>176.8434753417969</v>
       </c>
       <c r="C187" t="n">
         <v>198.6199951171875</v>
@@ -5348,7 +5348,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>186.6463470458984</v>
+        <v>186.6463623046875</v>
       </c>
       <c r="C188" t="n">
         <v>209.6300048828125</v>
@@ -5377,7 +5377,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>186.1210784912109</v>
+        <v>186.1210479736328</v>
       </c>
       <c r="C189" t="n">
         <v>209.0399932861328</v>
@@ -5406,7 +5406,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>178.8116455078125</v>
+        <v>178.8116149902344</v>
       </c>
       <c r="C190" t="n">
         <v>199.9199981689453</v>
@@ -5435,7 +5435,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>200.7874603271484</v>
+        <v>200.7874298095703</v>
       </c>
       <c r="C191" t="n">
         <v>224.4900054931641</v>
@@ -5464,7 +5464,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>206.5116882324219</v>
+        <v>206.51171875</v>
       </c>
       <c r="C192" t="n">
         <v>230.8899993896484</v>
@@ -5522,7 +5522,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>185.2238922119141</v>
+        <v>185.2239074707031</v>
       </c>
       <c r="C194" t="n">
         <v>206.1699981689453</v>
@@ -5551,7 +5551,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>183.6696624755859</v>
+        <v>183.6696319580078</v>
       </c>
       <c r="C195" t="n">
         <v>204.4400024414062</v>
@@ -5609,7 +5609,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>196.9906921386719</v>
+        <v>196.9907073974609</v>
       </c>
       <c r="C197" t="n">
         <v>218.1799926757812</v>
@@ -5638,7 +5638,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>201.2884216308594</v>
+        <v>201.2884368896484</v>
       </c>
       <c r="C198" t="n">
         <v>222.9400024414062</v>
@@ -5667,7 +5667,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>190.5420532226562</v>
+        <v>190.5419921875</v>
       </c>
       <c r="C199" t="n">
         <v>210.0399932861328</v>
@@ -5696,7 +5696,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>218.7368621826172</v>
+        <v>218.7368774414062</v>
       </c>
       <c r="C200" t="n">
         <v>241.1199951171875</v>
@@ -5725,7 +5725,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>221.7214660644531</v>
+        <v>221.7214813232422</v>
       </c>
       <c r="C201" t="n">
         <v>244.4100036621094</v>
@@ -5754,7 +5754,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>206.0795135498047</v>
+        <v>206.0794982910156</v>
       </c>
       <c r="C202" t="n">
         <v>226.1900024414062</v>
@@ -5783,7 +5783,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>220.2104949951172</v>
+        <v>220.2105102539062</v>
       </c>
       <c r="C203" t="n">
         <v>241.6999969482422</v>
@@ -5812,7 +5812,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>240.6553497314453</v>
+        <v>240.6553649902344</v>
       </c>
       <c r="C204" t="n">
         <v>264.1400146484375</v>
@@ -5870,7 +5870,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>206.7301635742188</v>
+        <v>206.7301788330078</v>
       </c>
       <c r="C206" t="n">
         <v>225.8099975585938</v>
@@ -5899,7 +5899,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>201.2463073730469</v>
+        <v>201.2462768554688</v>
       </c>
       <c r="C207" t="n">
         <v>219.8200073242188</v>
@@ -5928,7 +5928,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>204.9731140136719</v>
+        <v>204.97314453125</v>
       </c>
       <c r="C208" t="n">
         <v>222.6300048828125</v>
@@ -5957,7 +5957,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>202.5516967773438</v>
+        <v>202.5517272949219</v>
       </c>
       <c r="C209" t="n">
         <v>220</v>
@@ -5986,7 +5986,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>192.4149017333984</v>
+        <v>192.4149475097656</v>
       </c>
       <c r="C210" t="n">
         <v>208.9900054931641</v>
@@ -6015,7 +6015,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>203.5336608886719</v>
+        <v>203.5336761474609</v>
       </c>
       <c r="C211" t="n">
         <v>219.7899932861328</v>
@@ -6073,7 +6073,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>235.7783203125</v>
+        <v>235.7782897949219</v>
       </c>
       <c r="C213" t="n">
         <v>254.6100006103516</v>
@@ -6189,7 +6189,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>218.1327209472656</v>
+        <v>218.1327362060547</v>
       </c>
       <c r="C217" t="n">
         <v>232.9700012207031</v>
@@ -6218,7 +6218,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>230.1268920898438</v>
+        <v>230.1269073486328</v>
       </c>
       <c r="C218" t="n">
         <v>245.7799987792969</v>
@@ -6276,7 +6276,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>235.1854553222656</v>
+        <v>235.1854400634766</v>
       </c>
       <c r="C220" t="n">
         <v>249.7400054931641</v>
@@ -6305,7 +6305,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>227.7929382324219</v>
+        <v>227.7929077148438</v>
       </c>
       <c r="C221" t="n">
         <v>241.8899993896484</v>
@@ -6334,7 +6334,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>230.6463165283203</v>
+        <v>230.6463317871094</v>
       </c>
       <c r="C222" t="n">
         <v>244.9199981689453</v>
@@ -6363,7 +6363,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>226.0751342773438</v>
+        <v>226.0751190185547</v>
       </c>
       <c r="C223" t="n">
         <v>238.6900024414062</v>
@@ -6421,7 +6421,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>261.3280334472656</v>
+        <v>261.3280639648438</v>
       </c>
       <c r="C225" t="n">
         <v>275.9100036621094</v>
@@ -6450,7 +6450,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>263.429443359375</v>
+        <v>263.4294128417969</v>
       </c>
       <c r="C226" t="n">
         <v>276.7300109863281</v>
@@ -6479,7 +6479,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>275.338134765625</v>
+        <v>275.3381652832031</v>
       </c>
       <c r="C227" t="n">
         <v>289.239990234375</v>
@@ -6537,7 +6537,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>280.1042785644531</v>
+        <v>280.1043090820312</v>
       </c>
       <c r="C229" t="n">
         <v>292.7300109863281</v>
@@ -6595,7 +6595,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>301.5859680175781</v>
+        <v>301.5859985351562</v>
       </c>
       <c r="C231" t="n">
         <v>315.1799926757812</v>
@@ -6624,7 +6624,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>293.9100036621094</v>
+        <v>293.9100341796875</v>
       </c>
       <c r="C232" t="n">
         <v>305.5299987792969</v>
@@ -6682,7 +6682,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>313.1493835449219</v>
+        <v>313.1493530273438</v>
       </c>
       <c r="C234" t="n">
         <v>325.5299987792969</v>
@@ -6798,7 +6798,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>285.2221069335938</v>
+        <v>285.2220458984375</v>
       </c>
       <c r="C238" t="n">
         <v>293.5</v>
@@ -6856,7 +6856,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>248.0994720458984</v>
+        <v>248.0994873046875</v>
       </c>
       <c r="C240" t="n">
         <v>255.3000030517578</v>
@@ -6885,7 +6885,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>251.5909271240234</v>
+        <v>251.5909118652344</v>
       </c>
       <c r="C241" t="n">
         <v>257.2300109863281</v>
@@ -6943,7 +6943,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>209.6607055664062</v>
+        <v>209.6607208251953</v>
       </c>
       <c r="C243" t="n">
         <v>214.3600006103516</v>
